--- a/Result/profitability/5704.xlsx
+++ b/Result/profitability/5704.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>-0.3</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.04874999999999995</v>
+        <v>-0.105</v>
       </c>
       <c r="N2" t="n">
-        <v>42.9775</v>
+        <v>-70.92125000000001</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>-0.26</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.07374999999999995</v>
+        <v>-0.04999999999999995</v>
       </c>
       <c r="N3" t="n">
-        <v>48.38500000000001</v>
+        <v>-62.34</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>0.11</v>
       </c>
       <c r="M4" t="n">
-        <v>0.02750000000000004</v>
+        <v>-0.04249999999999995</v>
       </c>
       <c r="N4" t="n">
-        <v>57.24124999999999</v>
+        <v>-56.4725</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -1018,10 +1018,10 @@
         <v>-0.43</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.03249999999999996</v>
+        <v>-0.06499999999999995</v>
       </c>
       <c r="N5" t="n">
-        <v>63.0575</v>
+        <v>-49.1375</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,16 +1137,16 @@
         <v>0.19</v>
       </c>
       <c r="M6" t="n">
-        <v>0.02250000000000004</v>
+        <v>-0.07999999999999996</v>
       </c>
       <c r="N6" t="n">
-        <v>65.67125</v>
+        <v>-48.14750000000001</v>
       </c>
       <c r="O6" t="n">
         <v>1</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -1155,7 +1155,7 @@
         <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T6" t="n">
         <v>0</v>
@@ -1264,16 +1264,16 @@
         <v>0.02</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.01374999999999996</v>
+        <v>-0.1125</v>
       </c>
       <c r="N7" t="n">
-        <v>65.64625000000001</v>
+        <v>-49.20375000000001</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -1282,7 +1282,7 @@
         <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T7" t="n">
         <v>0</v>
@@ -1391,25 +1391,25 @@
         <v>0.22</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.02124999999999996</v>
+        <v>-0.12</v>
       </c>
       <c r="N8" t="n">
-        <v>63.905</v>
+        <v>-51.08875</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R8" t="n">
         <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T8" t="n">
         <v>0</v>
@@ -1521,7 +1521,7 @@
         <v>-0.06749999999999996</v>
       </c>
       <c r="N9" t="n">
-        <v>61.0375</v>
+        <v>61.03749999999999</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1775,7 +1775,7 @@
         <v>0.01375000000000003</v>
       </c>
       <c r="N11" t="n">
-        <v>49.78375</v>
+        <v>49.78374999999999</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1902,7 +1902,7 @@
         <v>0.02125000000000003</v>
       </c>
       <c r="N12" t="n">
-        <v>44.68000000000001</v>
+        <v>44.67999999999999</v>
       </c>
       <c r="O12" t="n">
         <v>1</v>
@@ -2029,7 +2029,7 @@
         <v>0.08125000000000004</v>
       </c>
       <c r="N13" t="n">
-        <v>39.09</v>
+        <v>39.08999999999999</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -9830,6 +9830,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>5704</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>2</v>
+      </c>
+      <c r="D75" t="n">
+        <v>23</v>
+      </c>
+      <c r="E75" t="n">
+        <v>-21</v>
+      </c>
+      <c r="F75" t="n">
+        <v>-870.86</v>
+      </c>
+      <c r="G75" t="n">
+        <v>-38</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>-1589.62%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>4</v>
+      </c>
+      <c r="J75" t="n">
+        <v>-34</v>
+      </c>
+      <c r="K75" t="n">
+        <v>-30</v>
+      </c>
+      <c r="L75" t="n">
+        <v>-0.51</v>
+      </c>
+      <c r="M75" t="n">
+        <v>-0.07499999999999996</v>
+      </c>
+      <c r="N75" t="n">
+        <v>-76.66499999999999</v>
+      </c>
+      <c r="O75" t="n">
+        <v>0</v>
+      </c>
+      <c r="P75" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>-0.79</v>
+      </c>
+      <c r="X75" t="n">
+        <v>-2.821428571428571</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-919.95</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-18.74006926054186</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>-0.26</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>-897.5600000000001</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-33.61647940074906</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS衰退 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
